--- a/Output/SUP/Malf_DLNM_SUP_model_fit_AIC_BIC_paper.xlsx
+++ b/Output/SUP/Malf_DLNM_SUP_model_fit_AIC_BIC_paper.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11020"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uccl0-my.sharepoint.com/personal/estela_blanco_uc_cl/Documents/Contaminación_Malformaciones Congénitas/Pollution_Malformation_TEM/Output/SUP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_0181658D02A276A61A464B52F37BD2728A47CA58" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82C7622D-3548-4C4B-B09D-714576C1A59B}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_66D26085819339B21C26537213B84BE3737CBC2A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1439AE3-7578-3442-9276-D6E04330EAF0}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Model_fit_paper" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Model_fit_paper!$A$1:$G$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Model_fit_paper!$A$1:$G$1</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
@@ -798,7 +798,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -833,7 +832,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -844,19 +843,19 @@
         <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -867,19 +866,19 @@
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -890,19 +889,19 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
         <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -913,19 +912,19 @@
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="G5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -936,19 +935,19 @@
         <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -962,16 +961,16 @@
         <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="G7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -985,16 +984,16 @@
         <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1008,16 +1007,16 @@
         <v>27</v>
       </c>
       <c r="E9" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="G9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -1031,16 +1030,16 @@
         <v>27</v>
       </c>
       <c r="E10" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="G10" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -1054,16 +1053,16 @@
         <v>27</v>
       </c>
       <c r="E11" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="G11" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1074,19 +1073,19 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -1097,19 +1096,19 @@
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="G13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -1120,19 +1119,19 @@
         <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E14" t="s">
         <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="G14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1143,19 +1142,19 @@
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E15" t="s">
         <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="G15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -1166,19 +1165,19 @@
         <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E16" t="s">
         <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="G16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -1201,7 +1200,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -1224,7 +1223,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -1247,7 +1246,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -1270,7 +1269,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -1293,7 +1292,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -1304,19 +1303,19 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E22" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="F22" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="G22" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -1327,19 +1326,19 @@
         <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E23" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="F23" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="G23" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>7</v>
       </c>
@@ -1350,19 +1349,19 @@
         <v>17</v>
       </c>
       <c r="D24" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E24" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="F24" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="G24" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -1373,19 +1372,19 @@
         <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E25" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="F25" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="G25" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>7</v>
       </c>
@@ -1396,19 +1395,19 @@
         <v>24</v>
       </c>
       <c r="D26" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E26" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="F26" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="G26" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>7</v>
       </c>
@@ -1431,7 +1430,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>7</v>
       </c>
@@ -1454,7 +1453,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>7</v>
       </c>
@@ -1477,7 +1476,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -1500,7 +1499,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>7</v>
       </c>
@@ -1534,16 +1533,16 @@
         <v>9</v>
       </c>
       <c r="D32" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E32" t="s">
         <v>11</v>
       </c>
       <c r="F32" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G32" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
@@ -1557,16 +1556,16 @@
         <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E33" t="s">
         <v>11</v>
       </c>
       <c r="F33" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="G33" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
@@ -1580,16 +1579,16 @@
         <v>17</v>
       </c>
       <c r="D34" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E34" t="s">
         <v>11</v>
       </c>
       <c r="F34" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="G34" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
@@ -1603,16 +1602,16 @@
         <v>20</v>
       </c>
       <c r="D35" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E35" t="s">
         <v>11</v>
       </c>
       <c r="F35" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="G35" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
@@ -1626,16 +1625,16 @@
         <v>24</v>
       </c>
       <c r="D36" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E36" t="s">
         <v>11</v>
       </c>
       <c r="F36" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
@@ -1652,13 +1651,13 @@
         <v>27</v>
       </c>
       <c r="E37" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="F37" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="G37" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
@@ -1675,13 +1674,13 @@
         <v>27</v>
       </c>
       <c r="E38" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="F38" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="G38" t="s">
-        <v>124</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
@@ -1698,13 +1697,13 @@
         <v>27</v>
       </c>
       <c r="E39" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="F39" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="G39" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
@@ -1721,13 +1720,13 @@
         <v>27</v>
       </c>
       <c r="E40" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="F40" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="G40" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
@@ -1744,13 +1743,13 @@
         <v>27</v>
       </c>
       <c r="E41" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="F41" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="G41" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
@@ -1764,16 +1763,16 @@
         <v>9</v>
       </c>
       <c r="D42" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E42" t="s">
         <v>11</v>
       </c>
       <c r="F42" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="G42" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
@@ -1787,16 +1786,16 @@
         <v>14</v>
       </c>
       <c r="D43" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E43" t="s">
         <v>11</v>
       </c>
       <c r="F43" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="G43" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
@@ -1810,16 +1809,16 @@
         <v>17</v>
       </c>
       <c r="D44" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E44" t="s">
         <v>11</v>
       </c>
       <c r="F44" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="G44" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
@@ -1833,16 +1832,16 @@
         <v>20</v>
       </c>
       <c r="D45" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E45" t="s">
         <v>11</v>
       </c>
       <c r="F45" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="G45" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
@@ -1856,16 +1855,16 @@
         <v>24</v>
       </c>
       <c r="D46" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E46" t="s">
         <v>11</v>
       </c>
       <c r="F46" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="G46" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
@@ -1994,16 +1993,16 @@
         <v>9</v>
       </c>
       <c r="D52" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E52" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="F52" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="G52" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
@@ -2017,16 +2016,16 @@
         <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E53" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="F53" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="G53" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
@@ -2040,16 +2039,16 @@
         <v>17</v>
       </c>
       <c r="D54" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E54" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="F54" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="G54" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
@@ -2063,16 +2062,16 @@
         <v>20</v>
       </c>
       <c r="D55" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E55" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="F55" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="G55" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
@@ -2086,16 +2085,16 @@
         <v>24</v>
       </c>
       <c r="D56" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E56" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="F56" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="G56" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
@@ -2214,16 +2213,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G61" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Congenital heart disease"/>
-      </filters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A32:G61">
-      <sortCondition ref="D1:D61"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:G1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>